--- a/work4-urgency/output/urgency_report.xlsx
+++ b/work4-urgency/output/urgency_report.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>

--- a/work4-urgency/output/urgency_report.xlsx
+++ b/work4-urgency/output/urgency_report.xlsx
@@ -12,7 +12,12 @@
     <sheet name="不良明細" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="判定基準と出典" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'サマリ'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'スパン別判定'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'不良明細'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'判定基準と出典'!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -444,12 +449,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -473,7 +478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -563,6 +568,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -570,23 +576,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
@@ -3359,6 +3365,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3366,17 +3373,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10627,6 +10634,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -10634,17 +10642,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12505,5 +12513,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/work4-urgency/output/urgency_report.xlsx
+++ b/work4-urgency/output/urgency_report.xlsx
@@ -567,6 +567,7 @@
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -3364,6 +3365,7 @@
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -10633,6 +10635,7 @@
       <c r="F330" t="inlineStr"/>
     </row>
   </sheetData>
+  <printOptions gridLines="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -10644,7 +10647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10653,6 +10656,8 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10686,6 +10691,16 @@
           <t>出典</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>出典資料</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>出典URL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10718,6 +10733,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10750,6 +10775,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10782,6 +10817,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10814,6 +10859,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10846,6 +10901,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10878,6 +10943,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10910,6 +10985,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10942,6 +11027,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10974,6 +11069,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11006,6 +11111,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11038,6 +11153,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11070,6 +11195,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11102,6 +11237,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11134,6 +11279,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11166,6 +11321,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11198,6 +11363,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11230,6 +11405,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11262,6 +11447,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -11294,6 +11489,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11326,6 +11531,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -11358,6 +11573,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -11390,6 +11615,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -11422,6 +11657,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11454,6 +11699,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -11486,6 +11741,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -11518,6 +11783,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -11550,6 +11825,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -11582,6 +11867,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -11614,6 +11909,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -11646,6 +11951,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -11678,6 +11993,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -11710,6 +12035,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -11742,6 +12077,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -11774,6 +12119,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -11806,6 +12161,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -11838,6 +12203,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -11870,6 +12245,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -11902,6 +12287,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -11934,6 +12329,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -11966,6 +12371,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -11998,6 +12413,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -12030,6 +12455,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12062,6 +12497,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -12094,6 +12539,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -12126,6 +12581,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -12158,6 +12623,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -12190,6 +12665,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -12222,6 +12707,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -12254,6 +12749,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -12286,6 +12791,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -12318,6 +12833,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -12350,6 +12875,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -12382,6 +12917,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -12414,6 +12959,16 @@
           <t>H21 表2.3(p.12)</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -12446,6 +13001,16 @@
           <t>H21 表2.8-2.9(p.15-16)</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -12478,6 +13043,16 @@
           <t>H21 表2.8-2.9(p.15-16)</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -12510,8 +13085,19 @@
           <t>H21 表2.8-2.9(p.15-16)</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/common/000044766.pdf</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <printOptions gridLines="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/work4-urgency/output/urgency_report.xlsx
+++ b/work4-urgency/output/urgency_report.xlsx
@@ -24,8 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +39,13 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -75,20 +85,29 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -476,10 +495,8 @@
           <t>判定実行日</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
+      <c r="B2" s="2" t="n">
+        <v>46257</v>
       </c>
     </row>
     <row r="3">
@@ -488,7 +505,7 @@
           <t>基準プロファイル</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>default_h21</t>
         </is>
@@ -500,7 +517,7 @@
           <t>判定スパン数</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="3" t="n">
         <v>60</v>
       </c>
     </row>
@@ -510,7 +527,7 @@
           <t>緊急度Ⅰ</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -520,7 +537,7 @@
           <t>緊急度Ⅱ</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="3" t="n">
         <v>28</v>
       </c>
     </row>
@@ -530,7 +547,7 @@
           <t>緊急度Ⅲ</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="3" t="n">
         <v>20</v>
       </c>
     </row>
@@ -540,7 +557,7 @@
           <t>異常なし</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -550,7 +567,7 @@
           <t>入力エラー件数</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -560,7 +577,7 @@
           <t>注意</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>本判定は国交省手引き(案)の判定例に準拠したデモであり、自治体の独自基準・維持管理指針本体とは異なる場合があります</t>
         </is>
@@ -704,12 +721,12 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>Ⅰ</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>破損a(管No.4, 8.0m) → 特例により発生率ランクA(備考②: 道路陥没等の社会的影響) / 腐食=A / たるみ=なし / ランクA×2・B×0 → 緊急度Ⅰ(ランクAが2項目以上)</t>
         </is>
@@ -751,12 +768,12 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>継手ズレa(管No.9, 18.4m) → 特例により発生率ランクA(備考②: 道路陥没等の社会的影響) / 腐食=なし / たるみ=なし / ランクA×1・B×0 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -798,12 +815,12 @@
         <v>23.5</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=23.5% / a+b=23.5% / a+b+c=23.5% → 発生率ランクA / 腐食=なし / たるみ=B / ランクA×1・B×1 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -841,12 +858,12 @@
         <v>18.8</v>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
         <is>
           <t>Ⅲ</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=18.8% / a+b=18.8% / a+b+c=18.8% → 発生率ランクB / 腐食=なし / たるみ=なし / ランクA×0・B×1 → 緊急度Ⅲ(ランクAがなく、ランクBが1項目もしくはランクCのみ)</t>
         </is>
@@ -888,12 +905,12 @@
         <v>2.9</v>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=2.9% / a+b=2.9% / a+b+c=2.9% → 発生率ランクB / 腐食=B / たるみ=なし / ランクA×0・B×2 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -935,12 +952,12 @@
         <v>17.6</v>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=0.0% / a+b=17.6% / a+b+c=17.6% → 発生率ランクB / 腐食=B / たるみ=なし / ランクA×0・B×2 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -978,12 +995,12 @@
         <v>64.7</v>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="L8" s="6" t="inlineStr">
         <is>
           <t>Ⅲ</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=0.0% / a+b=0.0% / a+b+c=64.7% → 発生率ランクB / 腐食=なし / たるみ=なし / ランクA×0・B×1 → 緊急度Ⅲ(ランクAがなく、ランクBが1項目もしくはランクCのみ)</t>
         </is>
@@ -1021,12 +1038,12 @@
         <v>12.5</v>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="L9" s="6" t="inlineStr">
         <is>
           <t>Ⅲ</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=0.0% / a+b=0.0% / a+b+c=12.5% → 発生率ランクC / 腐食=なし / たるみ=なし / ランクA×0・B×0 → 緊急度Ⅲ(ランクAがなく、ランクBが1項目もしくはランクCのみ)</t>
         </is>
@@ -1064,12 +1081,12 @@
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L10" s="6" t="inlineStr">
         <is>
           <t>Ⅲ</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>腐食=なし / たるみ=C / ランクA×0・B×0 → 緊急度Ⅲ(ランクAがなく、ランクBが1項目もしくはランクCのみ)</t>
         </is>
@@ -1108,7 +1125,7 @@
           <t>異常なし</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>腐食=なし / たるみ=なし / ランクA×0・B×0 → 緊急度異常なし(3項目とも異常なし)</t>
         </is>
@@ -1154,12 +1171,12 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>Ⅰ</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>破損a(管No.17, 35.5m) → 特例により発生率ランクA(備考②: 道路陥没等の社会的影響) / 腐食=A / たるみ=なし / ランクA×2・B×0 → 緊急度Ⅰ(ランクAが2項目以上)</t>
         </is>
@@ -1201,12 +1218,12 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>継手ズレa(管No.12, 24.8m) → 特例により発生率ランクA(備考②: 道路陥没等の社会的影響) / 腐食=なし / たるみ=なし / ランクA×1・B×0 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -1248,12 +1265,12 @@
         <v>25</v>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=25.0% / a+b=25.0% / a+b+c=25.0% → 発生率ランクA / 腐食=なし / たるみ=B / ランクA×1・B×1 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -1291,12 +1308,12 @@
         <v>19.1</v>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="L15" s="6" t="inlineStr">
         <is>
           <t>Ⅲ</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=19.1% / a+b=19.1% / a+b+c=19.1% → 発生率ランクB / 腐食=なし / たるみ=なし / ランクA×0・B×1 → 緊急度Ⅲ(ランクAがなく、ランクBが1項目もしくはランクCのみ)</t>
         </is>
@@ -1338,12 +1355,12 @@
         <v>1.8</v>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=1.8% / a+b=1.8% / a+b+c=1.8% → 発生率ランクB / 腐食=B / たるみ=なし / ランクA×0・B×2 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -1385,12 +1402,12 @@
         <v>17.9</v>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=0.0% / a+b=17.9% / a+b+c=17.9% → 発生率ランクB / 腐食=B / たるみ=なし / ランクA×0・B×2 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -1428,12 +1445,12 @@
         <v>65.40000000000001</v>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="L18" s="6" t="inlineStr">
         <is>
           <t>Ⅲ</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M18" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=0.0% / a+b=0.0% / a+b+c=65.4% → 発生率ランクB / 腐食=なし / たるみ=なし / ランクA×0・B×1 → 緊急度Ⅲ(ランクAがなく、ランクBが1項目もしくはランクCのみ)</t>
         </is>
@@ -1471,12 +1488,12 @@
         <v>11.7</v>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L19" s="6" t="inlineStr">
         <is>
           <t>Ⅲ</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=0.0% / a+b=0.0% / a+b+c=11.7% → 発生率ランクC / 腐食=なし / たるみ=なし / ランクA×0・B×0 → 緊急度Ⅲ(ランクAがなく、ランクBが1項目もしくはランクCのみ)</t>
         </is>
@@ -1514,12 +1531,12 @@
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="L20" s="6" t="inlineStr">
         <is>
           <t>Ⅲ</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>腐食=なし / たるみ=C / ランクA×0・B×0 → 緊急度Ⅲ(ランクAがなく、ランクBが1項目もしくはランクCのみ)</t>
         </is>
@@ -1558,7 +1575,7 @@
           <t>異常なし</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t>腐食=なし / たるみ=なし / ランクA×0・B×0 → 緊急度異常なし(3項目とも異常なし)</t>
         </is>
@@ -1604,12 +1621,12 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>Ⅰ</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>破損a(管No.13, 26.2m) → 特例により発生率ランクA(備考②: 道路陥没等の社会的影響) / 腐食=A / たるみ=なし / ランクA×2・B×0 → 緊急度Ⅰ(ランクAが2項目以上)</t>
         </is>
@@ -1651,12 +1668,12 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M23" s="3" t="inlineStr">
         <is>
           <t>継手ズレa(管No.8, 16.9m) → 特例により発生率ランクA(備考②: 道路陥没等の社会的影響) / 腐食=なし / たるみ=なし / ランクA×1・B×0 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -1698,12 +1715,12 @@
         <v>28.6</v>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" s="3" t="inlineStr">
+      <c r="L24" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M24" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=28.6% / a+b=28.6% / a+b+c=28.6% → 発生率ランクA / 腐食=なし / たるみ=B / ランクA×1・B×1 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -1741,12 +1758,12 @@
         <v>22.2</v>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" s="3" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M25" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=22.2% / a+b=22.2% / a+b+c=22.2% → 発生率ランクA / 腐食=なし / たるみ=なし / ランクA×1・B×0 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -1788,12 +1805,12 @@
         <v>5.6</v>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" s="3" t="inlineStr">
+      <c r="L26" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=5.6% / a+b=5.6% / a+b+c=5.6% → 発生率ランクB / 腐食=B / たるみ=なし / ランクA×0・B×2 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -1835,12 +1852,12 @@
         <v>20</v>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" s="3" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M27" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=0.0% / a+b=20.0% / a+b+c=20.0% → 発生率ランクB / 腐食=B / たるみ=なし / ランクA×0・B×2 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -1878,12 +1895,12 @@
         <v>65</v>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" s="4" t="inlineStr">
+      <c r="L28" s="6" t="inlineStr">
         <is>
           <t>Ⅲ</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M28" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=0.0% / a+b=0.0% / a+b+c=65.0% → 発生率ランクB / 腐食=なし / たるみ=なし / ランクA×0・B×1 → 緊急度Ⅲ(ランクAがなく、ランクBが1項目もしくはランクCのみ)</t>
         </is>
@@ -1921,12 +1938,12 @@
         <v>12.5</v>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" s="4" t="inlineStr">
+      <c r="L29" s="6" t="inlineStr">
         <is>
           <t>Ⅲ</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M29" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=0.0% / a+b=0.0% / a+b+c=12.5% → 発生率ランクC / 腐食=なし / たるみ=なし / ランクA×0・B×0 → 緊急度Ⅲ(ランクAがなく、ランクBが1項目もしくはランクCのみ)</t>
         </is>
@@ -1964,12 +1981,12 @@
         <v>0</v>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" s="4" t="inlineStr">
+      <c r="L30" s="6" t="inlineStr">
         <is>
           <t>Ⅲ</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M30" s="3" t="inlineStr">
         <is>
           <t>腐食=なし / たるみ=C / ランクA×0・B×0 → 緊急度Ⅲ(ランクAがなく、ランクBが1項目もしくはランクCのみ)</t>
         </is>
@@ -2008,7 +2025,7 @@
           <t>異常なし</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M31" s="3" t="inlineStr">
         <is>
           <t>腐食=なし / たるみ=なし / ランクA×0・B×0 → 緊急度異常なし(3項目とも異常なし)</t>
         </is>
@@ -2054,12 +2071,12 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L32" s="4" t="inlineStr">
         <is>
           <t>Ⅰ</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M32" s="3" t="inlineStr">
         <is>
           <t>破損a(管No.3, 7.4m) → 特例により発生率ランクA(備考②: 道路陥没等の社会的影響) / 腐食=A / たるみ=なし / ランクA×2・B×0 → 緊急度Ⅰ(ランクAが2項目以上)</t>
         </is>
@@ -2101,12 +2118,12 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L33" s="3" t="inlineStr">
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M33" s="3" t="inlineStr">
         <is>
           <t>継手ズレa(管No.10, 20.8m) → 特例により発生率ランクA(備考②: 道路陥没等の社会的影響) / 腐食=なし / たるみ=なし / ランクA×1・B×0 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -2148,12 +2165,12 @@
         <v>28.6</v>
       </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" s="3" t="inlineStr">
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M34" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=28.6% / a+b=28.6% / a+b+c=28.6% → 発生率ランクA / 腐食=なし / たるみ=B / ランクA×1・B×1 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -2191,12 +2208,12 @@
         <v>21.1</v>
       </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" s="3" t="inlineStr">
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M35" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=21.1% / a+b=21.1% / a+b+c=21.1% → 発生率ランクA / 腐食=なし / たるみ=なし / ランクA×1・B×0 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -2238,12 +2255,12 @@
         <v>25</v>
       </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" s="3" t="inlineStr">
+      <c r="L36" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M36" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=25.0% / a+b=25.0% / a+b+c=25.0% → 発生率ランクA / 腐食=B / たるみ=なし / ランクA×1・B×1 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -2285,12 +2302,12 @@
         <v>18.8</v>
       </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" s="3" t="inlineStr">
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M37" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=0.0% / a+b=18.8% / a+b+c=18.8% → 発生率ランクB / 腐食=B / たるみ=なし / ランクA×0・B×2 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -2328,12 +2345,12 @@
         <v>60</v>
       </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" s="4" t="inlineStr">
+      <c r="L38" s="6" t="inlineStr">
         <is>
           <t>Ⅲ</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M38" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=0.0% / a+b=0.0% / a+b+c=60.0% → 発生率ランクB / 腐食=なし / たるみ=なし / ランクA×0・B×1 → 緊急度Ⅲ(ランクAがなく、ランクBが1項目もしくはランクCのみ)</t>
         </is>
@@ -2371,12 +2388,12 @@
         <v>9.1</v>
       </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" s="4" t="inlineStr">
+      <c r="L39" s="6" t="inlineStr">
         <is>
           <t>Ⅲ</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M39" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=0.0% / a+b=0.0% / a+b+c=9.1% → 発生率ランクC / 腐食=なし / たるみ=なし / ランクA×0・B×0 → 緊急度Ⅲ(ランクAがなく、ランクBが1項目もしくはランクCのみ)</t>
         </is>
@@ -2414,12 +2431,12 @@
         <v>0</v>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" s="4" t="inlineStr">
+      <c r="L40" s="6" t="inlineStr">
         <is>
           <t>Ⅲ</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M40" s="3" t="inlineStr">
         <is>
           <t>腐食=なし / たるみ=C / ランクA×0・B×0 → 緊急度Ⅲ(ランクAがなく、ランクBが1項目もしくはランクCのみ)</t>
         </is>
@@ -2458,7 +2475,7 @@
           <t>異常なし</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M41" s="3" t="inlineStr">
         <is>
           <t>腐食=なし / たるみ=なし / ランクA×0・B×0 → 緊急度異常なし(3項目とも異常なし)</t>
         </is>
@@ -2504,12 +2521,12 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="L42" s="4" t="inlineStr">
         <is>
           <t>Ⅰ</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M42" s="3" t="inlineStr">
         <is>
           <t>破損a(管No.6, 12.7m) → 特例により発生率ランクA(備考②: 道路陥没等の社会的影響) / 腐食=A / たるみ=なし / ランクA×2・B×0 → 緊急度Ⅰ(ランクAが2項目以上)</t>
         </is>
@@ -2551,12 +2568,12 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L43" s="3" t="inlineStr">
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M43" s="3" t="inlineStr">
         <is>
           <t>継手ズレa(管No.33, 66.2m) → 特例により発生率ランクA(備考②: 道路陥没等の社会的影響) / 腐食=なし / たるみ=なし / ランクA×1・B×0 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -2598,12 +2615,12 @@
         <v>26.1</v>
       </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" s="3" t="inlineStr">
+      <c r="L44" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="M44" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=26.1% / a+b=26.1% / a+b+c=26.1% → 発生率ランクA / 腐食=なし / たるみ=B / ランクA×1・B×1 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -2641,12 +2658,12 @@
         <v>20.7</v>
       </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" s="3" t="inlineStr">
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M45" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=20.7% / a+b=20.7% / a+b+c=20.7% → 発生率ランクA / 腐食=なし / たるみ=なし / ランクA×1・B×0 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -2688,12 +2705,12 @@
         <v>4.3</v>
       </c>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" s="3" t="inlineStr">
+      <c r="L46" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M46" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=4.3% / a+b=4.3% / a+b+c=4.3% → 発生率ランクB / 腐食=B / たるみ=なし / ランクA×0・B×2 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -2735,12 +2752,12 @@
         <v>20</v>
       </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" s="3" t="inlineStr">
+      <c r="L47" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M47" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=0.0% / a+b=20.0% / a+b+c=20.0% → 発生率ランクB / 腐食=B / たるみ=なし / ランクA×0・B×2 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -2778,12 +2795,12 @@
         <v>64.7</v>
       </c>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" s="4" t="inlineStr">
+      <c r="L48" s="6" t="inlineStr">
         <is>
           <t>Ⅲ</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="M48" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=0.0% / a+b=0.0% / a+b+c=64.7% → 発生率ランクB / 腐食=なし / たるみ=なし / ランクA×0・B×1 → 緊急度Ⅲ(ランクAがなく、ランクBが1項目もしくはランクCのみ)</t>
         </is>
@@ -2821,12 +2838,12 @@
         <v>6.7</v>
       </c>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" s="4" t="inlineStr">
+      <c r="L49" s="6" t="inlineStr">
         <is>
           <t>Ⅲ</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M49" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=0.0% / a+b=0.0% / a+b+c=6.7% → 発生率ランクC / 腐食=なし / たるみ=なし / ランクA×0・B×0 → 緊急度Ⅲ(ランクAがなく、ランクBが1項目もしくはランクCのみ)</t>
         </is>
@@ -2864,12 +2881,12 @@
         <v>0</v>
       </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" s="4" t="inlineStr">
+      <c r="L50" s="6" t="inlineStr">
         <is>
           <t>Ⅲ</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="M50" s="3" t="inlineStr">
         <is>
           <t>腐食=なし / たるみ=C / ランクA×0・B×0 → 緊急度Ⅲ(ランクAがなく、ランクBが1項目もしくはランクCのみ)</t>
         </is>
@@ -2908,7 +2925,7 @@
           <t>異常なし</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="M51" s="3" t="inlineStr">
         <is>
           <t>腐食=なし / たるみ=なし / ランクA×0・B×0 → 緊急度異常なし(3項目とも異常なし)</t>
         </is>
@@ -2954,12 +2971,12 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr">
+      <c r="L52" s="4" t="inlineStr">
         <is>
           <t>Ⅰ</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="M52" s="3" t="inlineStr">
         <is>
           <t>破損a(管No.18, 36.1m) → 特例により発生率ランクA(備考②: 道路陥没等の社会的影響) / 腐食=A / たるみ=なし / ランクA×2・B×0 → 緊急度Ⅰ(ランクAが2項目以上)</t>
         </is>
@@ -3001,12 +3018,12 @@
           <t>○</t>
         </is>
       </c>
-      <c r="L53" s="3" t="inlineStr">
+      <c r="L53" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="M53" s="3" t="inlineStr">
         <is>
           <t>継手ズレa(管No.5, 10.3m) → 特例により発生率ランクA(備考②: 道路陥没等の社会的影響) / 腐食=なし / たるみ=なし / ランクA×1・B×0 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -3048,12 +3065,12 @@
         <v>50</v>
       </c>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" s="3" t="inlineStr">
+      <c r="L54" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="M54" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=50.0% / a+b=50.0% / a+b+c=50.0% → 発生率ランクA / 腐食=なし / たるみ=B / ランクA×1・B×1 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -3091,12 +3108,12 @@
         <v>22.2</v>
       </c>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" s="3" t="inlineStr">
+      <c r="L55" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="M55" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=22.2% / a+b=22.2% / a+b+c=22.2% → 発生率ランクA / 腐食=なし / たるみ=なし / ランクA×1・B×0 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -3138,12 +3155,12 @@
         <v>5.6</v>
       </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" s="3" t="inlineStr">
+      <c r="L56" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="M56" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=5.6% / a+b=5.6% / a+b+c=5.6% → 発生率ランクB / 腐食=B / たるみ=なし / ランクA×0・B×2 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -3185,12 +3202,12 @@
         <v>20</v>
       </c>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" s="3" t="inlineStr">
+      <c r="L57" s="5" t="inlineStr">
         <is>
           <t>Ⅱ</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="M57" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=0.0% / a+b=20.0% / a+b+c=20.0% → 発生率ランクB / 腐食=B / たるみ=なし / ランクA×0・B×2 → 緊急度Ⅱ(ランクAが1項目 もしくは ランクBが2項目以上)</t>
         </is>
@@ -3228,12 +3245,12 @@
         <v>64.8</v>
       </c>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" s="4" t="inlineStr">
+      <c r="L58" s="6" t="inlineStr">
         <is>
           <t>Ⅲ</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="M58" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=0.0% / a+b=0.0% / a+b+c=64.8% → 発生率ランクB / 腐食=なし / たるみ=なし / ランクA×0・B×1 → 緊急度Ⅲ(ランクAがなく、ランクBが1項目もしくはランクCのみ)</t>
         </is>
@@ -3271,12 +3288,12 @@
         <v>10</v>
       </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" s="4" t="inlineStr">
+      <c r="L59" s="6" t="inlineStr">
         <is>
           <t>Ⅲ</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="M59" s="3" t="inlineStr">
         <is>
           <t>不良発生率 a=0.0% / a+b=0.0% / a+b+c=10.0% → 発生率ランクC / 腐食=なし / たるみ=なし / ランクA×0・B×0 → 緊急度Ⅲ(ランクAがなく、ランクBが1項目もしくはランクCのみ)</t>
         </is>
@@ -3314,12 +3331,12 @@
         <v>0</v>
       </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" s="4" t="inlineStr">
+      <c r="L60" s="6" t="inlineStr">
         <is>
           <t>Ⅲ</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="M60" s="3" t="inlineStr">
         <is>
           <t>腐食=なし / たるみ=C / ランクA×0・B×0 → 緊急度Ⅲ(ランクAがなく、ランクBが1項目もしくはランクCのみ)</t>
         </is>
@@ -3358,7 +3375,7 @@
           <t>異常なし</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="M61" s="3" t="inlineStr">
         <is>
           <t>腐食=なし / たるみ=なし / ランクA×0・B×0 → 緊急度異常なし(3項目とも異常なし)</t>
         </is>
@@ -10723,7 +10740,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>鉄筋露出状態</t>
         </is>
@@ -10738,7 +10755,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -10765,7 +10782,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>骨材露出状態</t>
         </is>
@@ -10780,7 +10797,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -10807,7 +10824,7 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>表面が荒れた状態</t>
         </is>
@@ -10822,7 +10839,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -10849,7 +10866,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>内径以上</t>
         </is>
@@ -10864,7 +10881,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -10891,7 +10908,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>内径の1/2以上</t>
         </is>
@@ -10906,7 +10923,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -10933,7 +10950,7 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>内径の1/2未満</t>
         </is>
@@ -10948,7 +10965,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -10975,7 +10992,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>内径の1/2以上</t>
         </is>
@@ -10990,7 +11007,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11017,7 +11034,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>内径の1/4以上</t>
         </is>
@@ -11032,7 +11049,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11059,7 +11076,7 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>内径の1/4未満</t>
         </is>
@@ -11074,7 +11091,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11101,7 +11118,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>内径の1/4以上</t>
         </is>
@@ -11116,7 +11133,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11143,7 +11160,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>内径の1/8以上</t>
         </is>
@@ -11158,7 +11175,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11185,7 +11202,7 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>内径の1/8未満</t>
         </is>
@@ -11200,7 +11217,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11227,7 +11244,7 @@
           <t>a</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>欠落、軸方向のクラックで幅5mm以上</t>
         </is>
@@ -11242,7 +11259,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11269,7 +11286,7 @@
           <t>b</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>軸方向のクラックで幅2mm以上</t>
         </is>
@@ -11284,7 +11301,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11311,7 +11328,7 @@
           <t>c</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>軸方向のクラックで幅2mm未満</t>
         </is>
@@ -11326,7 +11343,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11353,7 +11370,7 @@
           <t>a</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>欠落、軸方向のクラックが管長の1/2以上</t>
         </is>
@@ -11368,7 +11385,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11395,7 +11412,7 @@
           <t>b</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>軸方向のクラックが管長の1/2未満</t>
         </is>
@@ -11410,7 +11427,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11437,7 +11454,7 @@
           <t>a</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>円周方向のクラックで幅5mm以上</t>
         </is>
@@ -11452,7 +11469,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11479,7 +11496,7 @@
           <t>b</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>円周方向のクラックで幅2mm以上</t>
         </is>
@@ -11494,7 +11511,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11521,7 +11538,7 @@
           <t>c</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>円周方向のクラックで幅2mm未満</t>
         </is>
@@ -11536,7 +11553,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11563,7 +11580,7 @@
           <t>a</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>円周方向のクラックで長さが円周の2/3以上</t>
         </is>
@@ -11578,7 +11595,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11605,7 +11622,7 @@
           <t>b</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>円周方向のクラックで長さが円周の2/3未満</t>
         </is>
@@ -11620,7 +11637,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11647,7 +11664,7 @@
           <t>a</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>脱却</t>
         </is>
@@ -11662,7 +11679,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11689,7 +11706,7 @@
           <t>b</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>70mm以上</t>
         </is>
@@ -11704,7 +11721,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11731,7 +11748,7 @@
           <t>c</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>70mm未満</t>
         </is>
@@ -11746,7 +11763,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11773,7 +11790,7 @@
           <t>a</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>脱却</t>
         </is>
@@ -11788,7 +11805,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11815,7 +11832,7 @@
           <t>b</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>50mm以上</t>
         </is>
@@ -11830,7 +11847,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11857,7 +11874,7 @@
           <t>c</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>50mm未満</t>
         </is>
@@ -11872,7 +11889,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11899,7 +11916,7 @@
           <t>a</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>噴き出ている</t>
         </is>
@@ -11914,7 +11931,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11941,7 +11958,7 @@
           <t>b</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>流れている</t>
         </is>
@@ -11956,7 +11973,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -11983,7 +12000,7 @@
           <t>c</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>にじんでいる</t>
         </is>
@@ -11998,7 +12015,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12025,7 +12042,7 @@
           <t>a</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>噴き出ている</t>
         </is>
@@ -12040,7 +12057,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12067,7 +12084,7 @@
           <t>b</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>流れている</t>
         </is>
@@ -12082,7 +12099,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12109,7 +12126,7 @@
           <t>c</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>にじんでいる</t>
         </is>
@@ -12124,7 +12141,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12151,7 +12168,7 @@
           <t>a</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>本管内径の1/2以上</t>
         </is>
@@ -12166,7 +12183,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12193,7 +12210,7 @@
           <t>b</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>本管内径の1/10以上</t>
         </is>
@@ -12208,7 +12225,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12235,7 +12252,7 @@
           <t>c</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>本管内径の1/10未満</t>
         </is>
@@ -12250,7 +12267,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12277,7 +12294,7 @@
           <t>a</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>本管内径の1/2以上</t>
         </is>
@@ -12292,7 +12309,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12319,7 +12336,7 @@
           <t>b</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>本管内径の1/10以上</t>
         </is>
@@ -12334,7 +12351,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12361,7 +12378,7 @@
           <t>c</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>本管内径の1/10未満</t>
         </is>
@@ -12376,7 +12393,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12403,7 +12420,7 @@
           <t>a</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>内径の1/2以上閉塞</t>
         </is>
@@ -12418,7 +12435,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12445,7 +12462,7 @@
           <t>b</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>内径の1/2未満閉塞</t>
         </is>
@@ -12460,7 +12477,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12487,7 +12504,7 @@
           <t>a</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>内径の1/2以上閉塞</t>
         </is>
@@ -12502,7 +12519,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12529,7 +12546,7 @@
           <t>b</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>内径の1/2未満閉塞</t>
         </is>
@@ -12544,7 +12561,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12571,7 +12588,7 @@
           <t>a</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>内径の1/2以上閉塞</t>
         </is>
@@ -12586,7 +12603,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12613,7 +12630,7 @@
           <t>b</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>内径の1/2未満閉塞</t>
         </is>
@@ -12628,7 +12645,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12655,7 +12672,7 @@
           <t>a</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>内径の1/2以上閉塞</t>
         </is>
@@ -12670,7 +12687,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12697,7 +12714,7 @@
           <t>b</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>内径の1/2未満閉塞</t>
         </is>
@@ -12712,7 +12729,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12739,7 +12756,7 @@
           <t>a</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>内径の3割以上</t>
         </is>
@@ -12754,7 +12771,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12781,7 +12798,7 @@
           <t>b</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>内径の1割以上</t>
         </is>
@@ -12796,7 +12813,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12823,7 +12840,7 @@
           <t>c</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>内径の1割未満</t>
         </is>
@@ -12838,7 +12855,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12865,7 +12882,7 @@
           <t>a</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>内径の3割以上</t>
         </is>
@@ -12880,7 +12897,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12907,7 +12924,7 @@
           <t>b</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>内径の1割以上</t>
         </is>
@@ -12922,7 +12939,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12949,7 +12966,7 @@
           <t>c</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>内径の1割未満</t>
         </is>
@@ -12964,7 +12981,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -12991,7 +13008,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>ランクAが2項目以上(重度: 速やかに措置が必要)</t>
         </is>
@@ -13006,7 +13023,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H56" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -13033,7 +13050,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>ランクAが1項目 もしくは ランクBが2項目以上(中度: 簡易な対応により必要な措置を5年未満まで延長できる)</t>
         </is>
@@ -13048,7 +13065,7 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
@@ -13075,7 +13092,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>ランクAがなく、ランクBが1項目もしくはランクCのみ(軽度: 簡易な対応により必要な措置を5年以上に延長できる)</t>
         </is>
@@ -13090,13 +13107,72 @@
           <t>下水道長寿命化支援制度に関する手引き(案) 平成21年度版</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H58" s="7" t="inlineStr">
         <is>
           <t>https://www.mlit.go.jp/common/000044766.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId57"/>
+  </hyperlinks>
   <printOptions gridLines="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
